--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -887,8 +887,8 @@
       <c r="M14" s="14">
         <v>-100</v>
       </c>
-      <c r="N14" s="13" t="s">
-        <v>21</v>
+      <c r="N14" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -926,7 +926,7 @@
         <v>-50</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="14">
         <v>-66.666666666666</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J16" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K16" s="14">
-        <v>44.444444444444</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M16" s="14">
-        <v>-38.095238095238</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.734693877551</v>
+        <v>-86.554621848739</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>66.666666666666</v>
+        <v>183.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J17" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K17" s="14">
-        <v>-10.526315789473</v>
+        <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>-19.047619047619</v>
+        <v>-25</v>
       </c>
       <c r="M17" s="14">
-        <v>142.857142857143</v>
+        <v>110</v>
       </c>
       <c r="N17" s="14">
-        <v>-29.166666666666</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-80</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
         <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="14">
-        <v>-66.666666666666</v>
+        <v>-68.75</v>
       </c>
       <c r="I18" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J18" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K18" s="14">
-        <v>-64.705882352941</v>
+        <v>-60</v>
       </c>
       <c r="L18" s="14">
-        <v>-70</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M18" s="14">
-        <v>-86.956521739130</v>
+        <v>-84.313725490196</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.273291925465</v>
+        <v>-95.897435897435</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F19" s="15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="15">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H19" s="14">
-        <v>-40.425531914893</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="I19" s="15">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J19" s="15">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K19" s="14">
-        <v>-16.363636363636</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="L19" s="14">
-        <v>-29.230769230769</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M19" s="14">
-        <v>-13.207547169811</v>
+        <v>-14.0625</v>
       </c>
       <c r="N19" s="14">
-        <v>-38.666666666666</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>-75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>-22.222222222222</v>
+        <v>37.5</v>
       </c>
       <c r="I20" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J20" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K20" s="14">
+        <v>-23.809523809523</v>
+      </c>
+      <c r="L20" s="14">
         <v>-33.333333333333</v>
       </c>
-      <c r="L20" s="14">
-        <v>-50</v>
-      </c>
       <c r="M20" s="14">
-        <v>-33.333333333333</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.814432989690</v>
+        <v>-92.660550458715</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>40</v>
       </c>
       <c r="F21" s="17">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.966292134831</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="I21" s="17">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="J21" s="17">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.491525423728</v>
+        <v>-12.030075187969</v>
       </c>
       <c r="L21" s="18">
-        <v>-34.482758620689</v>
+        <v>-27.329192546583</v>
       </c>
       <c r="M21" s="18">
-        <v>-37.086092715231</v>
+        <v>-32.758620689655</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.882882882882</v>
+        <v>-81.944444444444</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-11.428571428571</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="G24" s="15">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H24" s="14">
-        <v>-12.5</v>
+        <v>-16.935483870967</v>
       </c>
       <c r="I24" s="15">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="J24" s="15">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="K24" s="14">
-        <v>-6.060606060606</v>
+        <v>-12.169312169312</v>
       </c>
       <c r="L24" s="14">
-        <v>-24.757281553398</v>
+        <v>-29.957805907173</v>
       </c>
       <c r="M24" s="14">
-        <v>59.793814432989</v>
+        <v>49.549549549549</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E25" s="14">
-        <v>-33.333333333333</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F25" s="15">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G25" s="15">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H25" s="14">
-        <v>-26.262626262626</v>
+        <v>-29.670329670329</v>
       </c>
       <c r="I25" s="15">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J25" s="15">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="K25" s="14">
-        <v>-26.724137931034</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="L25" s="14">
-        <v>-27.350427350427</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
         <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G26" s="15">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H26" s="14">
-        <v>-2.222222222222</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J26" s="15">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="K26" s="14">
-        <v>10.344827586206</v>
+        <v>13.636363636363</v>
       </c>
       <c r="L26" s="14">
-        <v>-23.809523809523</v>
+        <v>-23.469387755102</v>
       </c>
       <c r="M26" s="14">
-        <v>45.454545454545</v>
+        <v>50</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1415,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>5</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>350</v>
       </c>
       <c r="F28" s="15">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G28" s="15">
         <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>133.333333333333</v>
+        <v>433.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>14.285714285714</v>
+        <v>88.888888888888</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1578,8 +1578,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="14">
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,20 +1610,20 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="15">
         <v>1</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="15">
-        <v>2</v>
-      </c>
       <c r="G33" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="14">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -929,7 +929,7 @@
         <v>-50</v>
       </c>
       <c r="N15" s="14">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
         <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K16" s="14">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L16" s="14">
-        <v>6.666666666666</v>
+        <v>20</v>
       </c>
       <c r="M16" s="14">
-        <v>-30.434782608695</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.554621848739</v>
+        <v>-86.466165413533</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
-      </c>
-      <c r="D17" s="15">
-        <v>2</v>
-      </c>
-      <c r="E17" s="14">
-        <v>100</v>
+        <v>7</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G17" s="15">
         <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>183.333333333333</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J17" s="15">
         <v>21</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>-25</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M17" s="14">
-        <v>110</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-12.5</v>
+        <v>-6.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H18" s="14">
-        <v>-68.75</v>
+        <v>-60</v>
       </c>
       <c r="I18" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J18" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K18" s="14">
-        <v>-60</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="L18" s="14">
-        <v>-63.636363636363</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>-84.313725490196</v>
+        <v>-80.357142857142</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.897435897435</v>
+        <v>-95.196506550218</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>11</v>
+      </c>
+      <c r="D19" s="15">
         <v>8</v>
       </c>
-      <c r="D19" s="15">
-        <v>4</v>
-      </c>
       <c r="E19" s="14">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="F19" s="15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G19" s="15">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H19" s="14">
-        <v>-34.146341463414</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="I19" s="15">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J19" s="15">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.779661016949</v>
+        <v>-2.985074626865</v>
       </c>
       <c r="L19" s="14">
-        <v>-21.428571428571</v>
+        <v>-18.75</v>
       </c>
       <c r="M19" s="14">
-        <v>-14.0625</v>
+        <v>-8.450704225352</v>
       </c>
       <c r="N19" s="14">
-        <v>-37.5</v>
+        <v>-38.095238095238</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H20" s="14">
-        <v>37.5</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J20" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K20" s="14">
-        <v>-23.809523809523</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L20" s="14">
-        <v>-33.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M20" s="14">
-        <v>-15.789473684210</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.660550458715</v>
+        <v>-93.233082706766</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
         <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F21" s="17">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.814814814814</v>
+        <v>-7.594936708860</v>
       </c>
       <c r="I21" s="17">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="J21" s="17">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.030075187969</v>
+        <v>-4.729729729729</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.329192546583</v>
+        <v>-22.099447513812</v>
       </c>
       <c r="M21" s="18">
-        <v>-32.758620689655</v>
+        <v>-25.789473684210</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.944444444444</v>
+        <v>-81.664499349804</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,14 +1191,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E24" s="14">
-        <v>-45.833333333333</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="F24" s="15">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G24" s="15">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="H24" s="14">
-        <v>-16.935483870967</v>
+        <v>-21.804511278195</v>
       </c>
       <c r="I24" s="15">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="J24" s="15">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="K24" s="14">
-        <v>-12.169312169312</v>
+        <v>-16.379310344827</v>
       </c>
       <c r="L24" s="14">
-        <v>-29.957805907173</v>
+        <v>-28.148148148148</v>
       </c>
       <c r="M24" s="14">
-        <v>49.549549549549</v>
+        <v>57.723577235772</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D25" s="15">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E25" s="14">
-        <v>-61.538461538461</v>
+        <v>-59.375</v>
       </c>
       <c r="F25" s="15">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G25" s="15">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H25" s="14">
-        <v>-29.670329670329</v>
+        <v>-35.416666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="J25" s="15">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.232558139534</v>
+        <v>-35.403726708074</v>
       </c>
       <c r="L25" s="14">
-        <v>-31.818181818181</v>
+        <v>-30.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="15">
         <v>50</v>
       </c>
-      <c r="F26" s="15">
-        <v>43</v>
-      </c>
       <c r="G26" s="15">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I26" s="15">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J26" s="15">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K26" s="14">
-        <v>13.636363636363</v>
+        <v>19.736842105263</v>
       </c>
       <c r="L26" s="14">
-        <v>-23.469387755102</v>
+        <v>-14.150943396226</v>
       </c>
       <c r="M26" s="14">
-        <v>50</v>
+        <v>71.698113207547</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>433.333333333333</v>
+        <v>325</v>
       </c>
       <c r="I28" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>88.888888888888</v>
+        <v>90</v>
       </c>
       <c r="L28" s="14">
-        <v>112.5</v>
+        <v>137.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,23 +1478,23 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>1</v>
       </c>
       <c r="G29" s="15">
         <v>1</v>
       </c>
       <c r="H29" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
+        <v>1</v>
       </c>
       <c r="J29" s="15">
         <v>1</v>
       </c>
       <c r="K29" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1503,15 +1503,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,23 +1519,23 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="15">
         <v>1</v>
       </c>
       <c r="H30" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I30" s="15">
+        <v>1</v>
       </c>
       <c r="J30" s="15">
         <v>1</v>
       </c>
       <c r="K30" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1544,7 +1544,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1561,7 +1561,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1622,11 +1622,11 @@
       <c r="F33" s="15">
         <v>1</v>
       </c>
-      <c r="G33" s="15">
-        <v>1</v>
-      </c>
-      <c r="H33" s="14">
-        <v>0</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="15">
         <v>2</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -914,7 +914,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -923,13 +923,13 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>6</v>
+      </c>
+      <c r="D16" s="15">
         <v>1</v>
       </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>500</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>-40</v>
+        <v>37.5</v>
       </c>
       <c r="I16" s="15">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="14">
-        <v>28.571428571428</v>
+        <v>60</v>
       </c>
       <c r="L16" s="14">
-        <v>20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M16" s="14">
-        <v>-21.739130434782</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.466165413533</v>
+        <v>-84.713375796178</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="D17" s="15">
+        <v>5</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
       </c>
       <c r="F17" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G17" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H17" s="14">
-        <v>233.333333333333</v>
+        <v>187.5</v>
       </c>
       <c r="I17" s="15">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J17" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K17" s="14">
-        <v>33.333333333333</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L17" s="14">
-        <v>-17.647058823529</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M17" s="14">
-        <v>133.333333333333</v>
+        <v>200</v>
       </c>
       <c r="N17" s="14">
-        <v>-6.666666666666</v>
+        <v>5.882352941176</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="15">
         <v>15</v>
       </c>
       <c r="H18" s="14">
-        <v>-60</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K18" s="14">
-        <v>-52.173913043478</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L18" s="14">
-        <v>-54.166666666666</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="M18" s="14">
-        <v>-80.357142857142</v>
+        <v>-80</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.196506550218</v>
+        <v>-95.121951219512</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E19" s="14">
-        <v>37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" s="15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H19" s="14">
-        <v>-15.789473684210</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="I19" s="15">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J19" s="15">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="K19" s="14">
-        <v>-2.985074626865</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="L19" s="14">
-        <v>-18.75</v>
+        <v>-24.489795918367</v>
       </c>
       <c r="M19" s="14">
-        <v>-8.450704225352</v>
+        <v>-3.896103896103</v>
       </c>
       <c r="N19" s="14">
-        <v>-38.095238095238</v>
+        <v>-36.206896551724</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
         <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H20" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K20" s="14">
-        <v>-21.739130434782</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="L20" s="14">
-        <v>-30.769230769230</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="M20" s="14">
-        <v>-14.285714285714</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.233082706766</v>
+        <v>-93.559322033898</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>60</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.594936708860</v>
+        <v>2.439024390243</v>
       </c>
       <c r="I21" s="17">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="J21" s="17">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.729729729729</v>
+        <v>-5.113636363636</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.099447513812</v>
+        <v>-20.853080568720</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.789473684210</v>
+        <v>-20.853080568720</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.664499349804</v>
+        <v>-80.467836257309</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1191,29 +1191,29 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-100</v>
+      <c r="F22" s="15">
+        <v>3</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J22" s="15">
         <v>1</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="M22" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D24" s="15">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E24" s="14">
-        <v>-37.209302325581</v>
+        <v>-64.102564102564</v>
       </c>
       <c r="F24" s="15">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="G24" s="15">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H24" s="14">
-        <v>-21.804511278195</v>
+        <v>-41.843971631205</v>
       </c>
       <c r="I24" s="15">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="J24" s="15">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="K24" s="14">
-        <v>-16.379310344827</v>
+        <v>-23.985239852398</v>
       </c>
       <c r="L24" s="14">
-        <v>-28.148148148148</v>
+        <v>-33.974358974359</v>
       </c>
       <c r="M24" s="14">
-        <v>57.723577235772</v>
+        <v>50.364963503649</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E25" s="14">
-        <v>-59.375</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F25" s="15">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="G25" s="15">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H25" s="14">
-        <v>-35.416666666666</v>
+        <v>-55.882352941176</v>
       </c>
       <c r="I25" s="15">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J25" s="15">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="K25" s="14">
-        <v>-35.403726708074</v>
+        <v>-41.489361702127</v>
       </c>
       <c r="L25" s="14">
-        <v>-30.666666666666</v>
+        <v>-39.560439560439</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>60</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F26" s="15">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G26" s="15">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H26" s="14">
-        <v>42.857142857142</v>
+        <v>48.717948717948</v>
       </c>
       <c r="I26" s="15">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="J26" s="15">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="K26" s="14">
-        <v>19.736842105263</v>
+        <v>23.595505617977</v>
       </c>
       <c r="L26" s="14">
-        <v>-14.150943396226</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="M26" s="14">
-        <v>71.698113207547</v>
+        <v>86.440677966101</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="J27" s="15">
+        <v>1</v>
+      </c>
+      <c r="K27" s="14">
+        <v>200</v>
       </c>
       <c r="L27" s="14">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F28" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G28" s="15">
         <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="I28" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L28" s="14">
-        <v>137.5</v>
+        <v>175</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1481,11 +1481,11 @@
       <c r="F29" s="15">
         <v>1</v>
       </c>
-      <c r="G29" s="15">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14">
-        <v>0</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="15">
         <v>1</v>
@@ -1510,8 +1510,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1522,11 +1522,11 @@
       <c r="F30" s="15">
         <v>1</v>
       </c>
-      <c r="G30" s="15">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14">
-        <v>0</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
@@ -1560,8 +1560,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>2</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -895,41 +895,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="H15" s="14">
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="J15" s="15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="14">
+        <v>200</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N15" s="14">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F16" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>37.5</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I16" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" s="14">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="L16" s="14">
-        <v>33.333333333333</v>
+        <v>30</v>
       </c>
       <c r="M16" s="14">
-        <v>-14.285714285714</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.713375796178</v>
+        <v>-84.883720930232</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
         <v>23</v>
       </c>
       <c r="G17" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H17" s="14">
-        <v>187.5</v>
+        <v>130</v>
       </c>
       <c r="I17" s="15">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J17" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K17" s="14">
-        <v>38.461538461538</v>
+        <v>41.379310344827</v>
       </c>
       <c r="L17" s="14">
-        <v>-5.263157894736</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="M17" s="14">
-        <v>200</v>
+        <v>141.176470588235</v>
       </c>
       <c r="N17" s="14">
-        <v>5.882352941176</v>
+        <v>13.888888888888</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-53.333333333333</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I18" s="15">
         <v>12</v>
       </c>
       <c r="J18" s="15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K18" s="14">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="L18" s="14">
-        <v>-53.846153846153</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M18" s="14">
-        <v>-80</v>
+        <v>-81.25</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.121951219512</v>
+        <v>-95.488721804511</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D19" s="15">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E19" s="14">
-        <v>-33.333333333333</v>
+        <v>500</v>
       </c>
       <c r="F19" s="15">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G19" s="15">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H19" s="14">
-        <v>-12.820512820512</v>
+        <v>34.482758620689</v>
       </c>
       <c r="I19" s="15">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J19" s="15">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K19" s="14">
-        <v>-9.756097560975</v>
+        <v>2.380952380952</v>
       </c>
       <c r="L19" s="14">
-        <v>-24.489795918367</v>
+        <v>-21.818181818181</v>
       </c>
       <c r="M19" s="14">
-        <v>-3.896103896103</v>
+        <v>3.614457831325</v>
       </c>
       <c r="N19" s="14">
-        <v>-36.206896551724</v>
+        <v>-35.338345864661</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>5</v>
+      </c>
+      <c r="D20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
       <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>400</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G20" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H20" s="14">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J20" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" s="14">
-        <v>-26.923076923076</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L20" s="14">
-        <v>-34.482758620689</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="14">
-        <v>-29.629629629629</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.559322033898</v>
+        <v>-92.771084337349</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,78 +1142,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.571428571428</v>
+        <v>118.181818181818</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G21" s="17">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>2.439024390243</v>
+        <v>37.681159420289</v>
       </c>
       <c r="I21" s="17">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="J21" s="17">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.113636363636</v>
+        <v>2.673796791443</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.853080568720</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.853080568720</v>
+        <v>-16.521739130434</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.467836257309</v>
+        <v>-79.725448785638</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
+        <v>2</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="15">
         <v>3</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
-        <v>3</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="15">
-        <v>4</v>
       </c>
       <c r="J22" s="15">
         <v>1</v>
       </c>
       <c r="K22" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L22" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M22" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D24" s="15">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E24" s="14">
-        <v>-64.102564102564</v>
+        <v>-62</v>
       </c>
       <c r="F24" s="15">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G24" s="15">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="H24" s="14">
-        <v>-41.843971631205</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I24" s="15">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="J24" s="15">
-        <v>271</v>
+        <v>321</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.985239852398</v>
+        <v>-29.906542056074</v>
       </c>
       <c r="L24" s="14">
-        <v>-33.974358974359</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="M24" s="14">
-        <v>50.364963503649</v>
+        <v>41.509433962264</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D25" s="15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E25" s="14">
-        <v>-77.777777777777</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="15">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G25" s="15">
         <v>102</v>
       </c>
       <c r="H25" s="14">
-        <v>-55.882352941176</v>
+        <v>-63.725490196078</v>
       </c>
       <c r="I25" s="15">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J25" s="15">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="K25" s="14">
-        <v>-41.489361702127</v>
+        <v>-44.036697247706</v>
       </c>
       <c r="L25" s="14">
-        <v>-39.560439560439</v>
+        <v>-34.054054054054</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>38.461538461538</v>
+        <v>112.5</v>
       </c>
       <c r="F26" s="15">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G26" s="15">
         <v>39</v>
       </c>
       <c r="H26" s="14">
-        <v>48.717948717948</v>
+        <v>64.102564102564</v>
       </c>
       <c r="I26" s="15">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="J26" s="15">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K26" s="14">
-        <v>23.595505617977</v>
+        <v>29.896907216494</v>
       </c>
       <c r="L26" s="14">
-        <v>-4.347826086956</v>
+        <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>86.440677966101</v>
+        <v>80</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L27" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>3</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G28" s="15">
         <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>375</v>
+        <v>275</v>
       </c>
       <c r="I28" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="15">
         <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>100</v>
+        <v>109.090909090909</v>
       </c>
       <c r="L28" s="14">
-        <v>175</v>
+        <v>187.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1479,7 +1479,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1488,13 +1488,13 @@
         <v>21</v>
       </c>
       <c r="I29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="15">
         <v>1</v>
       </c>
       <c r="K29" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1503,15 +1503,15 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1520,7 +1520,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1529,13 +1529,13 @@
         <v>21</v>
       </c>
       <c r="I30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="15">
         <v>1</v>
       </c>
       <c r="K30" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1544,7 +1544,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1619,8 +1619,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="15">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -908,22 +908,22 @@
         <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>3</v>
       </c>
       <c r="J15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L15" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
         <v>50</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>85.714285714285</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J16" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16" s="14">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="L16" s="14">
-        <v>30</v>
+        <v>17.391304347826</v>
       </c>
       <c r="M16" s="14">
-        <v>-13.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.883720930232</v>
+        <v>-85.789473684210</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F17" s="15">
         <v>23</v>
       </c>
       <c r="G17" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H17" s="14">
-        <v>130</v>
+        <v>155.555555555556</v>
       </c>
       <c r="I17" s="15">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J17" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K17" s="14">
-        <v>41.379310344827</v>
+        <v>53.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>-6.818181818181</v>
+        <v>-16.363636363636</v>
       </c>
       <c r="M17" s="14">
-        <v>141.176470588235</v>
+        <v>142.105263157895</v>
       </c>
       <c r="N17" s="14">
-        <v>13.888888888888</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
         <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>-53.846153846153</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I18" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K18" s="14">
-        <v>-60</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="L18" s="14">
-        <v>-57.142857142857</v>
+        <v>-56.25</v>
       </c>
       <c r="M18" s="14">
-        <v>-81.25</v>
+        <v>-79.411764705882</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.488721804511</v>
+        <v>-95.104895104895</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D19" s="15">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>500</v>
+        <v>144.444444444444</v>
       </c>
       <c r="F19" s="15">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G19" s="15">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H19" s="14">
-        <v>34.482758620689</v>
+        <v>58.823529411764</v>
       </c>
       <c r="I19" s="15">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="J19" s="15">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="K19" s="14">
-        <v>2.380952380952</v>
+        <v>16.129032258064</v>
       </c>
       <c r="L19" s="14">
-        <v>-21.818181818181</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M19" s="14">
-        <v>3.614457831325</v>
+        <v>22.727272727272</v>
       </c>
       <c r="N19" s="14">
-        <v>-35.338345864661</v>
+        <v>-22.857142857142</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>400</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
         <v>9</v>
       </c>
       <c r="H20" s="14">
-        <v>33.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I20" s="15">
         <v>24</v>
       </c>
       <c r="J20" s="15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K20" s="14">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>-17.241379310344</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.771084337349</v>
+        <v>-93.123209169054</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>118.181818181818</v>
+        <v>70.588235294117</v>
       </c>
       <c r="F21" s="17">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H21" s="18">
-        <v>37.681159420289</v>
+        <v>45.070422535211</v>
       </c>
       <c r="I21" s="17">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="J21" s="17">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="K21" s="18">
-        <v>2.673796791443</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.644067796610</v>
+        <v>-16.541353383458</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.521739130434</v>
+        <v>-13.28125</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.725448785638</v>
+        <v>-78.084896347482</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,10 +1210,10 @@
         <v>200</v>
       </c>
       <c r="L22" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D24" s="15">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E24" s="14">
-        <v>-62</v>
+        <v>30.555555555555</v>
       </c>
       <c r="F24" s="15">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="G24" s="15">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="H24" s="14">
-        <v>-53.846153846153</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="I24" s="15">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="J24" s="15">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="K24" s="14">
-        <v>-29.906542056074</v>
+        <v>-24.089635854341</v>
       </c>
       <c r="L24" s="14">
-        <v>-30.555555555555</v>
+        <v>-25.138121546961</v>
       </c>
       <c r="M24" s="14">
-        <v>41.509433962264</v>
+        <v>49.723756906077</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25" s="15">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E25" s="14">
-        <v>-60</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G25" s="15">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H25" s="14">
-        <v>-63.725490196078</v>
+        <v>-57.009345794392</v>
       </c>
       <c r="I25" s="15">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="J25" s="15">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="K25" s="14">
-        <v>-44.036697247706</v>
+        <v>-41.949152542372</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.054054054054</v>
+        <v>-33.816425120772</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>112.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G26" s="15">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H26" s="14">
-        <v>64.102564102564</v>
+        <v>76.744186046511</v>
       </c>
       <c r="I26" s="15">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="J26" s="15">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="K26" s="14">
-        <v>29.896907216494</v>
+        <v>37.614678899082</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>5.633802816901</v>
       </c>
       <c r="M26" s="14">
-        <v>80</v>
+        <v>108.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1400,22 +1400,22 @@
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
       </c>
       <c r="J27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,23 +1428,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>6</v>
+      </c>
+      <c r="G28" s="15">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>15</v>
-      </c>
-      <c r="G28" s="15">
-        <v>4</v>
-      </c>
       <c r="H28" s="14">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="I28" s="15">
         <v>23</v>
@@ -1456,7 +1456,7 @@
         <v>109.090909090909</v>
       </c>
       <c r="L28" s="14">
-        <v>187.5</v>
+        <v>155.555555555556</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1470,7 +1470,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1479,7 +1479,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1488,13 +1488,13 @@
         <v>21</v>
       </c>
       <c r="I29" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="15">
         <v>1</v>
       </c>
       <c r="K29" s="14">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1503,7 +1503,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,7 +1520,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1529,13 +1529,13 @@
         <v>21</v>
       </c>
       <c r="I30" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="15">
         <v>1</v>
       </c>
       <c r="K30" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1544,7 +1544,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="15">
+        <v>1</v>
+      </c>
+      <c r="K31" s="14">
+        <v>200</v>
       </c>
       <c r="L31" s="14">
         <v>200</v>
@@ -1610,8 +1610,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="15">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1619,8 +1619,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="15">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1629,13 +1629,13 @@
         <v>21</v>
       </c>
       <c r="I33" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="15">
         <v>2</v>
       </c>
       <c r="K33" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -881,8 +881,8 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="14">
+        <v>-100</v>
       </c>
       <c r="M14" s="14">
         <v>-100</v>
@@ -895,41 +895,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J15" s="15">
         <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>-57.142857142857</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>5</v>
+      </c>
+      <c r="D16" s="15">
         <v>1</v>
       </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>400</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>66.666666666666</v>
+        <v>180</v>
       </c>
       <c r="I16" s="15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J16" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="14">
-        <v>50</v>
+        <v>68.421052631578</v>
       </c>
       <c r="L16" s="14">
-        <v>17.391304347826</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M16" s="14">
-        <v>-30.769230769230</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.789473684210</v>
+        <v>-84.761904761904</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>200</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F17" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H17" s="14">
-        <v>155.555555555556</v>
+        <v>31.25</v>
       </c>
       <c r="I17" s="15">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J17" s="15">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K17" s="14">
-        <v>53.333333333333</v>
+        <v>40.540540540540</v>
       </c>
       <c r="L17" s="14">
-        <v>-16.363636363636</v>
+        <v>-14.754098360655</v>
       </c>
       <c r="M17" s="14">
-        <v>142.105263157895</v>
+        <v>147.619047619048</v>
       </c>
       <c r="N17" s="14">
-        <v>15</v>
+        <v>20.930232558139</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>-45.454545454545</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="15">
         <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" s="14">
-        <v>-54.838709677419</v>
+        <v>-56.25</v>
       </c>
       <c r="L18" s="14">
-        <v>-56.25</v>
+        <v>-57.575757575757</v>
       </c>
       <c r="M18" s="14">
-        <v>-79.411764705882</v>
+        <v>-80.281690140845</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.104895104895</v>
+        <v>-95.692307692307</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>144.444444444444</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G19" s="15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H19" s="14">
-        <v>58.823529411764</v>
+        <v>39.473684210526</v>
       </c>
       <c r="I19" s="15">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="J19" s="15">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="K19" s="14">
-        <v>16.129032258064</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L19" s="14">
-        <v>-7.692307692307</v>
+        <v>-13.533834586466</v>
       </c>
       <c r="M19" s="14">
-        <v>22.727272727272</v>
+        <v>21.052631578947</v>
       </c>
       <c r="N19" s="14">
-        <v>-22.857142857142</v>
+        <v>-22.297297297297</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
         <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>-11.111111111111</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I20" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J20" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K20" s="14">
-        <v>-20</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L20" s="14">
-        <v>-33.333333333333</v>
+        <v>-35</v>
       </c>
       <c r="M20" s="14">
-        <v>-31.428571428571</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.123209169054</v>
+        <v>-93.139841688654</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>70.588235294117</v>
+        <v>-12</v>
       </c>
       <c r="F21" s="17">
         <v>103</v>
       </c>
       <c r="G21" s="17">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H21" s="18">
-        <v>45.070422535211</v>
+        <v>27.160493827160</v>
       </c>
       <c r="I21" s="17">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="J21" s="17">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="K21" s="18">
-        <v>8.823529411764</v>
+        <v>6.986899563318</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.541353383458</v>
+        <v>-17.785234899328</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.28125</v>
+        <v>-10.583941605839</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.084896347482</v>
+        <v>-78.007181328545</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,35 +1185,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>2</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14">
+        <v>100</v>
       </c>
       <c r="I22" s="15">
         <v>3</v>
       </c>
       <c r="J22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D24" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E24" s="14">
-        <v>30.555555555555</v>
+        <v>-27.5</v>
       </c>
       <c r="F24" s="15">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G24" s="15">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H24" s="14">
-        <v>-38.095238095238</v>
+        <v>-34.545454545454</v>
       </c>
       <c r="I24" s="15">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="J24" s="15">
-        <v>357</v>
+        <v>397</v>
       </c>
       <c r="K24" s="14">
-        <v>-24.089635854341</v>
+        <v>-24.433249370277</v>
       </c>
       <c r="L24" s="14">
-        <v>-25.138121546961</v>
+        <v>-23.273657289002</v>
       </c>
       <c r="M24" s="14">
-        <v>49.723756906077</v>
+        <v>52.284263959390</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D25" s="15">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E25" s="14">
-        <v>-16.666666666666</v>
+        <v>-62.962962962963</v>
       </c>
       <c r="F25" s="15">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G25" s="15">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H25" s="14">
-        <v>-57.009345794392</v>
+        <v>-57.843137254902</v>
       </c>
       <c r="I25" s="15">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="J25" s="15">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="K25" s="14">
-        <v>-41.949152542372</v>
+        <v>-44.106463878327</v>
       </c>
       <c r="L25" s="14">
-        <v>-33.816425120772</v>
+        <v>-31.308411214953</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>66.666666666666</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G26" s="15">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H26" s="14">
-        <v>76.744186046511</v>
+        <v>52.083333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="J26" s="15">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="K26" s="14">
-        <v>37.614678899082</v>
+        <v>32.258064516129</v>
       </c>
       <c r="L26" s="14">
-        <v>5.633802816901</v>
+        <v>10.067114093959</v>
       </c>
       <c r="M26" s="14">
-        <v>108.333333333333</v>
+        <v>102.469135802469</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
         <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J27" s="15">
         <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>33.333333333333</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L27" s="14">
-        <v>-33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J28" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="14">
-        <v>109.090909090909</v>
+        <v>69.230769230769</v>
       </c>
       <c r="L28" s="14">
-        <v>155.555555555556</v>
+        <v>144.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1479,7 +1479,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1496,8 +1496,8 @@
       <c r="K29" s="14">
         <v>300</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="14">
+        <v>100</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1510,8 +1510,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1520,7 +1520,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1537,8 +1537,8 @@
       <c r="K30" s="14">
         <v>200</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="14">
+        <v>200</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1610,8 +1610,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="15">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,13 +905,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>6</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F16" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G16" s="15">
         <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="I16" s="15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J16" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="14">
-        <v>68.421052631578</v>
+        <v>80</v>
       </c>
       <c r="L16" s="14">
-        <v>23.076923076923</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M16" s="14">
-        <v>-23.809523809523</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.761904761904</v>
+        <v>-84.415584415584</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,78 +981,78 @@
         <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-42.857142857142</v>
+        <v>300</v>
       </c>
       <c r="F17" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G17" s="15">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>31.25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J17" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K17" s="14">
-        <v>40.540540540540</v>
+        <v>50</v>
       </c>
       <c r="L17" s="14">
-        <v>-14.754098360655</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="M17" s="14">
-        <v>147.619047619048</v>
+        <v>128</v>
       </c>
       <c r="N17" s="14">
-        <v>20.930232558139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>3</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>-66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J18" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" s="14">
-        <v>-56.25</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="L18" s="14">
-        <v>-57.575757575757</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="M18" s="14">
-        <v>-80.281690140845</v>
+        <v>-77.631578947368</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.692307692307</v>
+        <v>-95.417789757412</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
         <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>-16.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" s="15">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H19" s="14">
-        <v>39.473684210526</v>
+        <v>54.285714285714</v>
       </c>
       <c r="I19" s="15">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J19" s="15">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="K19" s="14">
-        <v>9.523809523809</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L19" s="14">
-        <v>-13.533834586466</v>
+        <v>-11.267605633802</v>
       </c>
       <c r="M19" s="14">
-        <v>21.052631578947</v>
+        <v>23.529411764705</v>
       </c>
       <c r="N19" s="14">
-        <v>-22.297297297297</v>
+        <v>-24.096385542168</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1104,37 +1104,37 @@
         <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H20" s="14">
-        <v>-27.272727272727</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J20" s="15">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K20" s="14">
-        <v>-23.529411764705</v>
+        <v>-27.5</v>
       </c>
       <c r="L20" s="14">
-        <v>-35</v>
+        <v>-36.956521739130</v>
       </c>
       <c r="M20" s="14">
-        <v>-31.578947368421</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.139841688654</v>
+        <v>-93.078758949880</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G21" s="17">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>27.160493827160</v>
+        <v>33.783783783783</v>
       </c>
       <c r="I21" s="17">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="J21" s="17">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="K21" s="18">
-        <v>6.986899563318</v>
+        <v>8.4</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.785234899328</v>
+        <v>-14.240506329113</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.583941605839</v>
+        <v>-7.508532423208</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.007181328545</v>
+        <v>-78.371907422186</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,20 +1185,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="15">
-        <v>2</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>3</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D24" s="15">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.5</v>
+        <v>-31.25</v>
       </c>
       <c r="F24" s="15">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G24" s="15">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="H24" s="14">
-        <v>-34.545454545454</v>
+        <v>-27.215189873417</v>
       </c>
       <c r="I24" s="15">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="J24" s="15">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="K24" s="14">
-        <v>-24.433249370277</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="L24" s="14">
-        <v>-23.273657289002</v>
+        <v>-24.941176470588</v>
       </c>
       <c r="M24" s="14">
-        <v>52.284263959390</v>
+        <v>47.004608294930</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>10</v>
       </c>
       <c r="D25" s="15">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>-62.962962962963</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F25" s="15">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G25" s="15">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H25" s="14">
-        <v>-57.843137254902</v>
+        <v>-45.348837209302</v>
       </c>
       <c r="I25" s="15">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="J25" s="15">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="K25" s="14">
-        <v>-44.106463878327</v>
+        <v>-42.700729927007</v>
       </c>
       <c r="L25" s="14">
-        <v>-31.308411214953</v>
+        <v>-33.474576271186</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D26" s="15">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>6.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G26" s="15">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H26" s="14">
-        <v>52.083333333333</v>
+        <v>69.047619047619</v>
       </c>
       <c r="I26" s="15">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="J26" s="15">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K26" s="14">
-        <v>32.258064516129</v>
+        <v>35.877862595419</v>
       </c>
       <c r="L26" s="14">
-        <v>10.067114093959</v>
+        <v>14.838709677419</v>
       </c>
       <c r="M26" s="14">
-        <v>102.469135802469</v>
+        <v>104.597701149425</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,13 +1397,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>7</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>5</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
       <c r="E28" s="14">
-        <v>-50</v>
+        <v>400</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G28" s="15">
         <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>33.333333333333</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J28" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>69.230769230769</v>
+        <v>92.857142857142</v>
       </c>
       <c r="L28" s="14">
-        <v>144.444444444444</v>
+        <v>200</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1579,7 +1579,7 @@
         <v>200</v>
       </c>
       <c r="L31" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>2</v>
@@ -914,22 +914,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>200</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N15" s="14">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
         <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="I16" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J16" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" s="14">
-        <v>80</v>
+        <v>80.952380952380</v>
       </c>
       <c r="L16" s="14">
-        <v>33.333333333333</v>
+        <v>31.034482758620</v>
       </c>
       <c r="M16" s="14">
-        <v>-18.181818181818</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.415584415584</v>
+        <v>-84.552845528455</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>300</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H17" s="14">
-        <v>33.333333333333</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I17" s="15">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J17" s="15">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="K17" s="14">
-        <v>50</v>
+        <v>28.260869565217</v>
       </c>
       <c r="L17" s="14">
-        <v>-9.523809523809</v>
+        <v>-15.714285714285</v>
       </c>
       <c r="M17" s="14">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="N17" s="14">
-        <v>0</v>
+        <v>-3.278688524590</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
         <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>-16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J18" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K18" s="14">
-        <v>-48.484848484848</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>-48.484848484848</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="M18" s="14">
-        <v>-77.631578947368</v>
+        <v>-73.076923076923</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.417789757412</v>
+        <v>-94.710327455919</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="15">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G19" s="15">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H19" s="14">
-        <v>54.285714285714</v>
+        <v>16.279069767441</v>
       </c>
       <c r="I19" s="15">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J19" s="15">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K19" s="14">
-        <v>7.692307692307</v>
+        <v>5.511811023622</v>
       </c>
       <c r="L19" s="14">
-        <v>-11.267605633802</v>
+        <v>-12.418300653594</v>
       </c>
       <c r="M19" s="14">
-        <v>23.529411764705</v>
+        <v>27.619047619047</v>
       </c>
       <c r="N19" s="14">
-        <v>-24.096385542168</v>
+        <v>-24.293785310734</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G20" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H20" s="14">
+        <v>-58.823529411764</v>
+      </c>
+      <c r="I20" s="15">
+        <v>30</v>
+      </c>
+      <c r="J20" s="15">
+        <v>44</v>
+      </c>
+      <c r="K20" s="14">
+        <v>-31.818181818181</v>
+      </c>
+      <c r="L20" s="14">
+        <v>-38.775510204081</v>
+      </c>
+      <c r="M20" s="14">
         <v>-28.571428571428</v>
       </c>
-      <c r="I20" s="15">
-        <v>29</v>
-      </c>
-      <c r="J20" s="15">
-        <v>40</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-27.5</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-36.956521739130</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-25.641025641025</v>
-      </c>
       <c r="N20" s="14">
-        <v>-93.078758949880</v>
+        <v>-93.492407809110</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="H21" s="18">
-        <v>33.783783783783</v>
+        <v>1.111111111111</v>
       </c>
       <c r="I21" s="17">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="J21" s="17">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="K21" s="18">
-        <v>8.4</v>
+        <v>4.332129963898</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.240506329113</v>
+        <v>-15</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.508532423208</v>
+        <v>-4.620462046204</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.371907422186</v>
+        <v>-78.608438193930</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,17 +1185,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1204,10 +1204,10 @@
         <v>3</v>
       </c>
       <c r="J22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D24" s="15">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E24" s="14">
-        <v>-31.25</v>
+        <v>-32.608695652173</v>
       </c>
       <c r="F24" s="15">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G24" s="15">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H24" s="14">
-        <v>-27.215189873417</v>
+        <v>-16.883116883116</v>
       </c>
       <c r="I24" s="15">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="J24" s="15">
-        <v>429</v>
+        <v>475</v>
       </c>
       <c r="K24" s="14">
-        <v>-25.641025641025</v>
+        <v>-26.526315789473</v>
       </c>
       <c r="L24" s="14">
-        <v>-24.941176470588</v>
+        <v>-21.923937360179</v>
       </c>
       <c r="M24" s="14">
-        <v>47.004608294930</v>
+        <v>50.431034482758</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E25" s="14">
-        <v>-9.090909090909</v>
+        <v>-72.413793103448</v>
       </c>
       <c r="F25" s="15">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G25" s="15">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H25" s="14">
-        <v>-45.348837209302</v>
+        <v>-49.411764705882</v>
       </c>
       <c r="I25" s="15">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="J25" s="15">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="K25" s="14">
-        <v>-42.700729927007</v>
+        <v>-45.544554455445</v>
       </c>
       <c r="L25" s="14">
-        <v>-33.474576271186</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F26" s="15">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G26" s="15">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H26" s="14">
-        <v>69.047619047619</v>
+        <v>27.659574468085</v>
       </c>
       <c r="I26" s="15">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="J26" s="15">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="K26" s="14">
-        <v>35.877862595419</v>
+        <v>30.555555555555</v>
       </c>
       <c r="L26" s="14">
-        <v>14.838709677419</v>
+        <v>11.904761904761</v>
       </c>
       <c r="M26" s="14">
-        <v>104.597701149425</v>
+        <v>97.894736842105</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
@@ -1406,16 +1406,16 @@
         <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L27" s="14">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
         <v>5</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>400</v>
-      </c>
-      <c r="F28" s="15">
-        <v>7</v>
       </c>
       <c r="G28" s="15">
         <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>133.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J28" s="15">
         <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>92.857142857142</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L28" s="14">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,7 +1479,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1520,7 +1520,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1551,8 +1551,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1560,26 +1560,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="15">
         <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="15">
         <v>1</v>
       </c>
       <c r="K31" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L31" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -898,20 +898,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
         <v>7</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G16" s="15">
         <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="I16" s="15">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J16" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K16" s="14">
-        <v>80.952380952380</v>
+        <v>86.956521739130</v>
       </c>
       <c r="L16" s="14">
-        <v>31.034482758620</v>
+        <v>26.470588235294</v>
       </c>
       <c r="M16" s="14">
-        <v>-17.391304347826</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.552845528455</v>
+        <v>-83.397683397683</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-75</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H17" s="14">
-        <v>-17.647058823529</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I17" s="15">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J17" s="15">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K17" s="14">
-        <v>28.260869565217</v>
+        <v>26.923076923076</v>
       </c>
       <c r="L17" s="14">
-        <v>-15.714285714285</v>
+        <v>-12</v>
       </c>
       <c r="M17" s="14">
-        <v>136</v>
+        <v>135.714285714286</v>
       </c>
       <c r="N17" s="14">
-        <v>-3.278688524590</v>
+        <v>-8.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="15">
+        <v>7</v>
+      </c>
+      <c r="G18" s="15">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
         <v>0</v>
       </c>
-      <c r="F18" s="15">
-        <v>8</v>
-      </c>
-      <c r="G18" s="15">
-        <v>6</v>
-      </c>
-      <c r="H18" s="14">
-        <v>33.333333333333</v>
-      </c>
       <c r="I18" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J18" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K18" s="14">
-        <v>-41.666666666666</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="L18" s="14">
-        <v>-38.235294117647</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M18" s="14">
-        <v>-73.076923076923</v>
+        <v>-74.418604651162</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.710327455919</v>
+        <v>-94.761904761904</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>-20</v>
+        <v>150</v>
       </c>
       <c r="F19" s="15">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G19" s="15">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H19" s="14">
-        <v>16.279069767441</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="J19" s="15">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K19" s="14">
-        <v>5.511811023622</v>
+        <v>9.923664122137</v>
       </c>
       <c r="L19" s="14">
-        <v>-12.418300653594</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M19" s="14">
-        <v>27.619047619047</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N19" s="14">
-        <v>-24.293785310734</v>
+        <v>-27.638190954773</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D20" s="15">
         <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-75</v>
+        <v>75</v>
       </c>
       <c r="F20" s="15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G20" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H20" s="14">
-        <v>-58.823529411764</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I20" s="15">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J20" s="15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K20" s="14">
-        <v>-31.818181818181</v>
+        <v>-22.916666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>-38.775510204081</v>
+        <v>-27.450980392156</v>
       </c>
       <c r="M20" s="14">
-        <v>-28.571428571428</v>
+        <v>-24.489795918367</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.492407809110</v>
+        <v>-92.570281124498</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-44.444444444444</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F21" s="17">
         <v>91</v>
       </c>
       <c r="G21" s="17">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" s="18">
-        <v>1.111111111111</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="J21" s="17">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="K21" s="18">
-        <v>4.332129963898</v>
+        <v>8.135593220338</v>
       </c>
       <c r="L21" s="18">
-        <v>-15</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.620462046204</v>
+        <v>-2.743902439024</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.608438193930</v>
+        <v>-78.105696636925</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,11 +1185,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" s="15">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E24" s="14">
-        <v>-32.608695652173</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="15">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="G24" s="15">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H24" s="14">
-        <v>-16.883116883116</v>
+        <v>-29.113924050632</v>
       </c>
       <c r="I24" s="15">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="J24" s="15">
-        <v>475</v>
+        <v>515</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.526315789473</v>
+        <v>-26.213592233009</v>
       </c>
       <c r="L24" s="14">
-        <v>-21.923937360179</v>
+        <v>-20.502092050209</v>
       </c>
       <c r="M24" s="14">
-        <v>50.431034482758</v>
+        <v>54.471544715447</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D25" s="15">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E25" s="14">
-        <v>-72.413793103448</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F25" s="15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G25" s="15">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H25" s="14">
-        <v>-49.411764705882</v>
+        <v>-45</v>
       </c>
       <c r="I25" s="15">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="J25" s="15">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="K25" s="14">
-        <v>-45.544554455445</v>
+        <v>-42.721518987341</v>
       </c>
       <c r="L25" s="14">
-        <v>-31.818181818181</v>
+        <v>-31.178707224334</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>-23.076923076923</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="15">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G26" s="15">
         <v>47</v>
       </c>
       <c r="H26" s="14">
-        <v>27.659574468085</v>
+        <v>10.638297872340</v>
       </c>
       <c r="I26" s="15">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="J26" s="15">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="K26" s="14">
-        <v>30.555555555555</v>
+        <v>27.564102564102</v>
       </c>
       <c r="L26" s="14">
-        <v>11.904761904761</v>
+        <v>6.989247311827</v>
       </c>
       <c r="M26" s="14">
-        <v>97.894736842105</v>
+        <v>80.909090909090</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,20 +1390,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
         <v>8</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,25 +1438,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="15">
         <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J28" s="15">
         <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>85.714285714285</v>
+        <v>100</v>
       </c>
       <c r="L28" s="14">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,8 +1478,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>2</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1519,8 +1519,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1551,8 +1551,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1563,11 +1563,11 @@
       <c r="F31" s="15">
         <v>1</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>0</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>4</v>
@@ -1619,8 +1619,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="15">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,31 +905,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="15">
         <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>133.333333333333</v>
+        <v>200</v>
       </c>
       <c r="L15" s="14">
-        <v>133.333333333333</v>
+        <v>200</v>
       </c>
       <c r="M15" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>150</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>180</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I16" s="15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J16" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" s="14">
-        <v>86.956521739130</v>
+        <v>69.230769230769</v>
       </c>
       <c r="L16" s="14">
-        <v>26.470588235294</v>
+        <v>25.714285714285</v>
       </c>
       <c r="M16" s="14">
-        <v>-6.521739130434</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-83.397683397683</v>
+        <v>-83.941605839416</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>16.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H17" s="14">
-        <v>-22.727272727272</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="I17" s="15">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J17" s="15">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K17" s="14">
-        <v>26.923076923076</v>
+        <v>20</v>
       </c>
       <c r="L17" s="14">
-        <v>-12</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M17" s="14">
-        <v>135.714285714286</v>
+        <v>132.258064516129</v>
       </c>
       <c r="N17" s="14">
-        <v>-8.333333333333</v>
+        <v>-8.860759493670</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
         <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I18" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" s="15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K18" s="14">
-        <v>-42.105263157894</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L18" s="14">
-        <v>-38.888888888888</v>
+        <v>-41.463414634146</v>
       </c>
       <c r="M18" s="14">
-        <v>-74.418604651162</v>
+        <v>-73.033707865168</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.761904761904</v>
+        <v>-94.690265486725</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>150</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G19" s="15">
         <v>38</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="I19" s="15">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="J19" s="15">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="K19" s="14">
-        <v>9.923664122137</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L19" s="14">
-        <v>-11.111111111111</v>
+        <v>-9.941520467836</v>
       </c>
       <c r="M19" s="14">
-        <v>28.571428571428</v>
+        <v>25.203252032520</v>
       </c>
       <c r="N19" s="14">
-        <v>-27.638190954773</v>
+        <v>-28.372093023255</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
         <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>75</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" s="15">
         <v>18</v>
       </c>
       <c r="H20" s="14">
-        <v>-27.777777777777</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J20" s="15">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K20" s="14">
-        <v>-22.916666666666</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="14">
-        <v>-27.450980392156</v>
+        <v>-29.090909090909</v>
       </c>
       <c r="M20" s="14">
-        <v>-24.489795918367</v>
+        <v>-33.898305084745</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.570281124498</v>
+        <v>-92.791127541589</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>66.666666666666</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="F21" s="17">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G21" s="17">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-7.216494845360</v>
       </c>
       <c r="I21" s="17">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="J21" s="17">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="K21" s="18">
-        <v>8.135593220338</v>
+        <v>4.907975460122</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.121212121212</v>
+        <v>-10.704960835509</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.743902439024</v>
+        <v>-4.469273743016</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.105696636925</v>
+        <v>-78.230426479949</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1195,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D24" s="15">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E24" s="14">
-        <v>-20</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G24" s="15">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="H24" s="14">
-        <v>-29.113924050632</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="I24" s="15">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="J24" s="15">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.213592233009</v>
+        <v>-23.908918406072</v>
       </c>
       <c r="L24" s="14">
-        <v>-20.502092050209</v>
+        <v>-19.639278557114</v>
       </c>
       <c r="M24" s="14">
-        <v>54.471544715447</v>
+        <v>51.893939393939</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D25" s="15">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>15.384615384615</v>
+        <v>150</v>
       </c>
       <c r="F25" s="15">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G25" s="15">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="H25" s="14">
-        <v>-45</v>
+        <v>-24.561403508771</v>
       </c>
       <c r="I25" s="15">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="J25" s="15">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K25" s="14">
-        <v>-42.721518987341</v>
+        <v>-40.625</v>
       </c>
       <c r="L25" s="14">
-        <v>-31.178707224334</v>
+        <v>-30.147058823529</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E26" s="14">
-        <v>-25</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F26" s="15">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G26" s="15">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H26" s="14">
-        <v>10.638297872340</v>
+        <v>2.040816326530</v>
       </c>
       <c r="I26" s="15">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="J26" s="15">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="K26" s="14">
-        <v>27.564102564102</v>
+        <v>23.699421965317</v>
       </c>
       <c r="L26" s="14">
-        <v>6.989247311827</v>
+        <v>5.940594059405</v>
       </c>
       <c r="M26" s="14">
-        <v>80.909090909090</v>
+        <v>81.355932203389</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="15">
         <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L27" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>7</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>133.333333333333</v>
+        <v>250</v>
       </c>
       <c r="I28" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J28" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>100</v>
+        <v>93.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>180</v>
+        <v>163.636363636364</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
       </c>
       <c r="I31" s="15">
         <v>4</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L31" s="14">
         <v>100</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -695,10 +695,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -896,7 +896,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,31 +905,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I15" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J15" s="15">
         <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>200</v>
+        <v>266.666666666667</v>
       </c>
       <c r="L15" s="14">
-        <v>200</v>
+        <v>266.666666666667</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>266.666666666667</v>
       </c>
       <c r="N15" s="14">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
         <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>42.857142857142</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I16" s="15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J16" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K16" s="14">
-        <v>69.230769230769</v>
+        <v>65.517241379310</v>
       </c>
       <c r="L16" s="14">
-        <v>25.714285714285</v>
+        <v>29.729729729729</v>
       </c>
       <c r="M16" s="14">
-        <v>-8.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N16" s="14">
-        <v>-83.941605839416</v>
+        <v>-83.391003460207</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-25</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G17" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H17" s="14">
-        <v>-17.391304347826</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="I17" s="15">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="J17" s="15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K17" s="14">
-        <v>20</v>
+        <v>27.692307692307</v>
       </c>
       <c r="L17" s="14">
-        <v>-5.263157894736</v>
+        <v>6.410256410256</v>
       </c>
       <c r="M17" s="14">
-        <v>132.258064516129</v>
+        <v>151.515151515152</v>
       </c>
       <c r="N17" s="14">
-        <v>-8.860759493670</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>3</v>
+      </c>
+      <c r="D18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
-        <v>4</v>
-      </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F18" s="15">
         <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>-10</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I18" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J18" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K18" s="14">
-        <v>-42.857142857142</v>
+        <v>-38.636363636363</v>
       </c>
       <c r="L18" s="14">
-        <v>-41.463414634146</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="M18" s="14">
-        <v>-73.033707865168</v>
+        <v>-70.967741935483</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.690265486725</v>
+        <v>-94.339622641509</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D19" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="14">
-        <v>-33.333333333333</v>
+        <v>30.769230769230</v>
       </c>
       <c r="F19" s="15">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G19" s="15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H19" s="14">
-        <v>-2.631578947368</v>
+        <v>20.512820512820</v>
       </c>
       <c r="I19" s="15">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="J19" s="15">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="K19" s="14">
-        <v>7.692307692307</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L19" s="14">
-        <v>-9.941520467836</v>
+        <v>-7.446808510638</v>
       </c>
       <c r="M19" s="14">
-        <v>25.203252032520</v>
+        <v>39.2</v>
       </c>
       <c r="N19" s="14">
-        <v>-28.372093023255</v>
+        <v>-23.348017621145</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
         <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H20" s="14">
-        <v>-33.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="I20" s="15">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J20" s="15">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K20" s="14">
         <v>-25</v>
       </c>
       <c r="L20" s="14">
-        <v>-29.090909090909</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M20" s="14">
-        <v>-33.898305084745</v>
+        <v>-31.147540983606</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.791127541589</v>
+        <v>-92.820512820512</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,78 +1142,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-32.258064516129</v>
+        <v>40.740740740740</v>
       </c>
       <c r="F21" s="17">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G21" s="17">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.216494845360</v>
+        <v>6.796116504854</v>
       </c>
       <c r="I21" s="17">
-        <v>342</v>
+        <v>385</v>
       </c>
       <c r="J21" s="17">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="K21" s="18">
-        <v>4.907975460122</v>
+        <v>9.065155807365</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.704960835509</v>
+        <v>-5.637254901960</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.469273743016</v>
+        <v>2.941176470588</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.230426479949</v>
+        <v>-76.959904248952</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>2</v>
+      </c>
+      <c r="D22" s="15">
+        <v>2</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15">
+        <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22" s="14">
         <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="14">
-        <v>-62.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E24" s="14">
-        <v>83.333333333333</v>
+        <v>-21.875</v>
       </c>
       <c r="F24" s="15">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G24" s="15">
         <v>130</v>
       </c>
       <c r="H24" s="14">
-        <v>-19.230769230769</v>
+        <v>-18.461538461538</v>
       </c>
       <c r="I24" s="15">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="J24" s="15">
-        <v>527</v>
+        <v>559</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.908918406072</v>
+        <v>-23.971377459749</v>
       </c>
       <c r="L24" s="14">
-        <v>-19.639278557114</v>
+        <v>-23.007246376811</v>
       </c>
       <c r="M24" s="14">
-        <v>51.893939393939</v>
+        <v>42.617449664429</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>10</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E25" s="14">
-        <v>150</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F25" s="15">
         <v>43</v>
       </c>
       <c r="G25" s="15">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H25" s="14">
-        <v>-24.561403508771</v>
+        <v>-27.118644067796</v>
       </c>
       <c r="I25" s="15">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J25" s="15">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="K25" s="14">
-        <v>-40.625</v>
+        <v>-39.939939939939</v>
       </c>
       <c r="L25" s="14">
-        <v>-30.147058823529</v>
+        <v>-34.853420195439</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>-17.647058823529</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F26" s="15">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G26" s="15">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H26" s="14">
-        <v>2.040816326530</v>
+        <v>-21.818181818181</v>
       </c>
       <c r="I26" s="15">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="J26" s="15">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="K26" s="14">
-        <v>23.699421965317</v>
+        <v>18.817204301075</v>
       </c>
       <c r="L26" s="14">
-        <v>5.940594059405</v>
+        <v>6.25</v>
       </c>
       <c r="M26" s="14">
-        <v>81.355932203389</v>
+        <v>74.015748031496</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I27" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" s="15">
         <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L27" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
         <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J28" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="14">
-        <v>93.333333333333</v>
+        <v>87.5</v>
       </c>
       <c r="L28" s="14">
-        <v>163.636363636364</v>
+        <v>150</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -898,38 +898,38 @@
       <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
+        <v>400</v>
+      </c>
+      <c r="I15" s="15">
+        <v>12</v>
+      </c>
+      <c r="J15" s="15">
+        <v>4</v>
+      </c>
+      <c r="K15" s="14">
+        <v>200</v>
+      </c>
+      <c r="L15" s="14">
         <v>300</v>
       </c>
-      <c r="I15" s="15">
-        <v>11</v>
-      </c>
-      <c r="J15" s="15">
-        <v>3</v>
-      </c>
-      <c r="K15" s="14">
-        <v>266.666666666667</v>
-      </c>
-      <c r="L15" s="14">
-        <v>266.666666666667</v>
-      </c>
       <c r="M15" s="14">
-        <v>266.666666666667</v>
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F16" s="15">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>22.222222222222</v>
+        <v>60</v>
       </c>
       <c r="I16" s="15">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J16" s="15">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K16" s="14">
-        <v>65.517241379310</v>
+        <v>74.193548387096</v>
       </c>
       <c r="L16" s="14">
-        <v>29.729729729729</v>
+        <v>31.707317073170</v>
       </c>
       <c r="M16" s="14">
-        <v>-11.111111111111</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="N16" s="14">
-        <v>-83.391003460207</v>
+        <v>-82.059800664451</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
         <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G17" s="15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H17" s="14">
-        <v>-3.703703703703</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J17" s="15">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K17" s="14">
-        <v>27.692307692307</v>
+        <v>27.142857142857</v>
       </c>
       <c r="L17" s="14">
-        <v>6.410256410256</v>
+        <v>8.536585365853</v>
       </c>
       <c r="M17" s="14">
-        <v>151.515151515152</v>
+        <v>147.222222222222</v>
       </c>
       <c r="N17" s="14">
-        <v>0</v>
+        <v>1.136363636363</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
         <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>-18.181818181818</v>
+        <v>20</v>
       </c>
       <c r="I18" s="15">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J18" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K18" s="14">
-        <v>-38.636363636363</v>
+        <v>-28.260869565217</v>
       </c>
       <c r="L18" s="14">
-        <v>-37.209302325581</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="M18" s="14">
-        <v>-70.967741935483</v>
+        <v>-64.893617021276</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.339622641509</v>
+        <v>-93.465346534653</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E19" s="14">
-        <v>30.769230769230</v>
+        <v>-45</v>
       </c>
       <c r="F19" s="15">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" s="15">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H19" s="14">
-        <v>20.512820512820</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="I19" s="15">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="J19" s="15">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="K19" s="14">
-        <v>11.538461538461</v>
+        <v>5.681818181818</v>
       </c>
       <c r="L19" s="14">
-        <v>-7.446808510638</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M19" s="14">
-        <v>39.2</v>
+        <v>44.186046511627</v>
       </c>
       <c r="N19" s="14">
-        <v>-23.348017621145</v>
+        <v>-21.518987341772</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" s="14">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G20" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H20" s="14">
-        <v>-18.75</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I20" s="15">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J20" s="15">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K20" s="14">
-        <v>-25</v>
+        <v>-24.193548387096</v>
       </c>
       <c r="L20" s="14">
-        <v>-26.315789473684</v>
+        <v>-21.666666666666</v>
       </c>
       <c r="M20" s="14">
-        <v>-31.147540983606</v>
+        <v>-24.193548387096</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.820512820512</v>
+        <v>-92.282430213464</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>40.740740740740</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G21" s="17">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="H21" s="18">
-        <v>6.796116504854</v>
+        <v>12.5</v>
       </c>
       <c r="I21" s="17">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="J21" s="17">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="K21" s="18">
-        <v>9.065155807365</v>
+        <v>8.226221079691</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.637254901960</v>
+        <v>-4.100227790432</v>
       </c>
       <c r="M21" s="18">
-        <v>2.941176470588</v>
+        <v>8.785529715762</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.959904248952</v>
+        <v>-75.942857142857</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,37 +1183,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
         <v>0</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15">
         <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="14">
         <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>66.666666666666</v>
+        <v>20</v>
       </c>
       <c r="M22" s="14">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D24" s="15">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E24" s="14">
-        <v>-21.875</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="F24" s="15">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G24" s="15">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="H24" s="14">
-        <v>-18.461538461538</v>
+        <v>-13.274336283185</v>
       </c>
       <c r="I24" s="15">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="J24" s="15">
-        <v>559</v>
+        <v>588</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.971377459749</v>
+        <v>-24.149659863945</v>
       </c>
       <c r="L24" s="14">
-        <v>-23.007246376811</v>
+        <v>-23.890784982935</v>
       </c>
       <c r="M24" s="14">
-        <v>42.617449664429</v>
+        <v>39.375</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>10</v>
       </c>
       <c r="D25" s="15">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E25" s="14">
-        <v>-23.076923076923</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="F25" s="15">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G25" s="15">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H25" s="14">
-        <v>-27.118644067796</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I25" s="15">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="J25" s="15">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="K25" s="14">
-        <v>-39.939939939939</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.853420195439</v>
+        <v>-37.349397590361</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E26" s="14">
-        <v>-38.461538461538</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G26" s="15">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="H26" s="14">
-        <v>-21.818181818181</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I26" s="15">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="J26" s="15">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="K26" s="14">
-        <v>18.817204301075</v>
+        <v>10</v>
       </c>
       <c r="L26" s="14">
-        <v>6.25</v>
+        <v>5.479452054794</v>
       </c>
       <c r="M26" s="14">
-        <v>74.015748031496</v>
+        <v>56.081081081081</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,32 +1390,32 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I27" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L27" s="14">
-        <v>100</v>
+        <v>116.666666666667</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,14 +1428,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>100</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>4</v>
@@ -1570,16 +1570,16 @@
         <v>0</v>
       </c>
       <c r="I31" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="15">
         <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L31" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-062pct.xlsx
+++ b/data/source/weekly/cs-en-us-062pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -896,40 +896,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I15" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="L15" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="N15" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E16" s="14">
-        <v>200</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F16" s="15">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H16" s="14">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="15">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J16" s="15">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K16" s="14">
-        <v>74.193548387096</v>
+        <v>44.736842105263</v>
       </c>
       <c r="L16" s="14">
-        <v>31.707317073170</v>
+        <v>27.906976744186</v>
       </c>
       <c r="M16" s="14">
-        <v>-5.263157894736</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="N16" s="14">
-        <v>-82.059800664451</v>
+        <v>-82.484076433121</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
         <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="15">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G17" s="15">
+        <v>23</v>
+      </c>
+      <c r="H17" s="14">
+        <v>8.695652173913</v>
+      </c>
+      <c r="I17" s="15">
+        <v>93</v>
+      </c>
+      <c r="J17" s="15">
+        <v>75</v>
+      </c>
+      <c r="K17" s="14">
         <v>24</v>
       </c>
-      <c r="H17" s="14">
-        <v>16.666666666666</v>
-      </c>
-      <c r="I17" s="15">
-        <v>89</v>
-      </c>
-      <c r="J17" s="15">
-        <v>70</v>
-      </c>
-      <c r="K17" s="14">
-        <v>27.142857142857</v>
-      </c>
       <c r="L17" s="14">
-        <v>8.536585365853</v>
+        <v>4.494382022471</v>
       </c>
       <c r="M17" s="14">
-        <v>147.222222222222</v>
+        <v>144.736842105263</v>
       </c>
       <c r="N17" s="14">
-        <v>1.136363636363</v>
+        <v>-5.102040816326</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>4</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>20</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I18" s="15">
         <v>33</v>
       </c>
       <c r="J18" s="15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K18" s="14">
-        <v>-28.260869565217</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="L18" s="14">
-        <v>-29.787234042553</v>
+        <v>-32.653061224489</v>
       </c>
       <c r="M18" s="14">
-        <v>-64.893617021276</v>
+        <v>-65.625</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.465346534653</v>
+        <v>-93.831775700934</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D19" s="15">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>-45</v>
+        <v>125</v>
       </c>
       <c r="F19" s="15">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G19" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H19" s="14">
-        <v>-2.040816326530</v>
+        <v>3.773584905660</v>
       </c>
       <c r="I19" s="15">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="J19" s="15">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="K19" s="14">
-        <v>5.681818181818</v>
+        <v>10.869565217391</v>
       </c>
       <c r="L19" s="14">
-        <v>-8.823529411764</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M19" s="14">
-        <v>44.186046511627</v>
+        <v>52.238805970149</v>
       </c>
       <c r="N19" s="14">
-        <v>-21.518987341772</v>
+        <v>-17.741935483871</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-16.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F20" s="15">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G20" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H20" s="14">
-        <v>-5.555555555555</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J20" s="15">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K20" s="14">
-        <v>-24.193548387096</v>
+        <v>-20.634920634920</v>
       </c>
       <c r="L20" s="14">
-        <v>-21.666666666666</v>
+        <v>-21.875</v>
       </c>
       <c r="M20" s="14">
-        <v>-24.193548387096</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.282430213464</v>
+        <v>-92.163009404388</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,78 +1142,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.111111111111</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F21" s="17">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G21" s="17">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H21" s="18">
-        <v>12.5</v>
+        <v>5.172413793103</v>
       </c>
       <c r="I21" s="17">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="J21" s="17">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="K21" s="18">
-        <v>8.226221079691</v>
+        <v>9.489051094890</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.100227790432</v>
+        <v>-3.433476394849</v>
       </c>
       <c r="M21" s="18">
-        <v>8.785529715762</v>
+        <v>11.940298507462</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.942857142857</v>
+        <v>-75.583288117200</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>3</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
       </c>
       <c r="J22" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L22" s="14">
         <v>20</v>
       </c>
       <c r="M22" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" s="14">
-        <v>-20.689655172413</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F24" s="15">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G24" s="15">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="H24" s="14">
-        <v>-13.274336283185</v>
+        <v>-16.831683168316</v>
       </c>
       <c r="I24" s="15">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="J24" s="15">
-        <v>588</v>
+        <v>616</v>
       </c>
       <c r="K24" s="14">
-        <v>-24.149659863945</v>
+        <v>-25.162337662337</v>
       </c>
       <c r="L24" s="14">
-        <v>-23.890784982935</v>
+        <v>-25.645161290322</v>
       </c>
       <c r="M24" s="14">
-        <v>39.375</v>
+        <v>36.390532544378</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="15">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E25" s="14">
-        <v>-47.368421052631</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F25" s="15">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G25" s="15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H25" s="14">
-        <v>-14.285714285714</v>
+        <v>-24</v>
       </c>
       <c r="I25" s="15">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="J25" s="15">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="K25" s="14">
-        <v>-40.909090909090</v>
+        <v>-40.710382513661</v>
       </c>
       <c r="L25" s="14">
-        <v>-37.349397590361</v>
+        <v>-38</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D26" s="15">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E26" s="14">
-        <v>-58.333333333333</v>
+        <v>-6.25</v>
       </c>
       <c r="F26" s="15">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G26" s="15">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H26" s="14">
-        <v>-36.363636363636</v>
+        <v>-30</v>
       </c>
       <c r="I26" s="15">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="J26" s="15">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="K26" s="14">
-        <v>10</v>
+        <v>9.734513274336</v>
       </c>
       <c r="L26" s="14">
-        <v>5.479452054794</v>
+        <v>7.826086956521</v>
       </c>
       <c r="M26" s="14">
-        <v>56.081081081081</v>
+        <v>55</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,34 +1388,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I27" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J27" s="15">
         <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="L27" s="14">
-        <v>116.666666666667</v>
+        <v>128.571428571429</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J28" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>87.5</v>
+        <v>88.235294117647</v>
       </c>
       <c r="L28" s="14">
-        <v>150</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
